--- a/artfynd/A 59543-2022 artfynd.xlsx
+++ b/artfynd/A 59543-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 59543-2022 artfynd.xlsx
+++ b/artfynd/A 59543-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>24946</v>
       </c>
       <c r="B2" t="n">
-        <v>57586</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58829</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494562.2110590432</v>
+        <v>494562</v>
       </c>
       <c r="R2" t="n">
-        <v>6428890.591930595</v>
+        <v>6428891</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2005-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2005-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -796,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>24947</v>
+        <v>68175900</v>
       </c>
       <c r="B3" t="n">
-        <v>57584</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58829</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,37 +792,54 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208242</v>
+        <v>100141</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Laurenti, 1768)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Säthälla, Efterlycke (1), Sm</t>
+          <t>Säthälla, Etterlycke, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494562.2110590432</v>
+        <v>494513</v>
       </c>
       <c r="R3" t="n">
-        <v>6428890.591930595</v>
+        <v>6428909</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,27 +863,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2005-01-01</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1998-04-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2005-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Lokal-Nr.: 120: Även förekomst av större vattensalamander</t>
+          <t>1998-04-28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,17 +883,241 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Anna Isaksson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Josefine Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Salamander inventering i Jönköpings län</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>24947</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58826</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>208242</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lissotriton vulgaris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Säthälla, Efterlycke (1), Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>494562</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6428891</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Tranås</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Tranås</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2005-12-31</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Lokal-Nr.: 120: Även förekomst av större vattensalamander</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Yvonne Liliegren</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Pål Mernelius</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Större vattensalamander I Jönköpings län 2004-2005</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>68175898</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58826</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>208242</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lissotriton vulgaris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Säthälla, Etterlycke, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>494513</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6428909</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Tranås</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Tranås</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>1998-04-28</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>1998-04-28</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anna Isaksson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Josefine Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Salamander inventering i Jönköpings län</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 59543-2022 artfynd.xlsx
+++ b/artfynd/A 59543-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Större vattensalamander I Jönköpings län 2004-2005</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/24946</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
           <t>Salamander inventering i Jönköpings län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68175900</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
           <t>Större vattensalamander I Jönköpings län 2004-2005</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/24947</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,8 +1140,19 @@
           <t>Salamander inventering i Jönköpings län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68175898</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>